--- a/Stats Sheet/Round Gaps/International.xlsx
+++ b/Stats Sheet/Round Gaps/International.xlsx
@@ -391,7 +391,7 @@
     <x:t>Arich</x:t>
   </x:si>
   <x:si>
-    <x:t>Kubaslov</x:t>
+    <x:t>Nikikula</x:t>
   </x:si>
   <x:si>
     <x:t>211</x:t>
